--- a/data/inst_5.xlsx
+++ b/data/inst_5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\flexible-vrp\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TFG\Flexible\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFD6F78F-2BB3-4AF2-8A5D-911C4018D3A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F537FCE7-64AE-4A18-AA5A-1467FC16CCC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5A598FCB-B967-4DAF-9410-AD9F1FA49DAC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{5A598FCB-B967-4DAF-9410-AD9F1FA49DAC}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="3" r:id="rId1"/>
@@ -503,9 +503,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -543,7 +543,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -649,7 +649,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -791,7 +791,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -800,12 +800,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118A7758-BA92-46A5-BE73-1AD0F0A01B68}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -813,7 +813,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -821,7 +821,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -829,7 +829,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -837,7 +837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -845,7 +845,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -853,7 +853,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -861,7 +861,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -869,7 +869,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -877,7 +877,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -885,7 +885,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -894,15 +894,15 @@
         <v>17.857142857142858</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -910,7 +910,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -926,9 +926,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A54DE7-45BC-48AF-A573-13FFF226C261}">
   <dimension ref="A1:C57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -939,7 +939,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -950,7 +950,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -961,7 +961,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -972,7 +972,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -983,7 +983,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -994,7 +994,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1082,7 +1082,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -1247,7 +1247,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -1269,7 +1269,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>7</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -1291,7 +1291,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>7</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>7</v>
       </c>
@@ -1324,7 +1324,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>3</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>3</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>3</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>3</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>8</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>8</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>8</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>8</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>8</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -1467,7 +1467,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>8</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>9</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>9</v>
       </c>
@@ -1500,7 +1500,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>9</v>
       </c>
@@ -1511,7 +1511,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>9</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -1544,7 +1544,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>9</v>
       </c>
@@ -1563,9 +1563,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E770ECA-E10C-4651-A068-F1B5FC905D1A}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1579,7 +1579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1711,6 +1711,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004EB831025BF00641AE88F2A902AAAF1B" ma:contentTypeVersion="2" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="922787e71b43b1c3ae0f2ec30aa8cf0c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a01b58d8-c5db-4160-879c-9baa1e9d5116" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="549c965bef73b0ff34fc7fce22a81277" ns2:_="">
     <xsd:import namespace="a01b58d8-c5db-4160-879c-9baa1e9d5116"/>
@@ -1842,22 +1857,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E555F8B-86CD-499D-908D-6C46A60A7E3A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4F665F3-1E57-4CCF-A68E-CA487352D404}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2589810-7BFA-47D4-83A1-6AC043710CE2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1873,21 +1890,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4F665F3-1E57-4CCF-A68E-CA487352D404}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E555F8B-86CD-499D-908D-6C46A60A7E3A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>